--- a/Aji_game copy_February.xlsx
+++ b/Aji_game copy_February.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sboora01/AJi_game project/Ajinomoto-conductor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6FAC39-DC23-4541-839B-5B65129D3DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA69AB9-CD88-FE48-B093-50C21CC18E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{21F6189A-E587-BD42-BB90-C9E09379CDC7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" activeTab="6" xr2:uid="{21F6189A-E587-BD42-BB90-C9E09379CDC7}"/>
   </bookViews>
   <sheets>
     <sheet name="User_funnel" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="133">
   <si>
     <t>event</t>
   </si>
@@ -825,6 +825,24 @@
   <si>
     <t>sum_total_duration_min</t>
   </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>aprils</t>
+  </si>
+  <si>
+    <t>avg(April)</t>
+  </si>
+  <si>
+    <t>AVG(April)</t>
+  </si>
+  <si>
+    <t>Avg(April)</t>
+  </si>
+  <si>
+    <t>total_duration_up</t>
+  </si>
 </sst>
 </file>
 
@@ -911,7 +929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -933,7 +951,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7773,10 +7790,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA68136C-BA99-B548-B374-5E32657D69F6}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7784,7 +7801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7794,8 +7811,11 @@
       <c r="C2">
         <v>644</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7805,8 +7825,11 @@
       <c r="C3">
         <v>565</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -7816,8 +7839,11 @@
       <c r="C4">
         <v>252</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -7826,6 +7852,9 @@
       </c>
       <c r="C5" t="s">
         <v>120</v>
+      </c>
+      <c r="D5" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -7836,10 +7865,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E47D239-6B24-8C4C-9A6C-CBD1ECF60961}">
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -7859,7 +7888,7 @@
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>45989</v>
       </c>
@@ -7884,8 +7913,11 @@
       <c r="K2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>45990</v>
       </c>
@@ -7914,8 +7946,12 @@
         <f>AVERAGE(D95:D123)</f>
         <v>2.9655172413793105</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L3">
+        <f>AVERAGE(D126:D145)</f>
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>45991</v>
       </c>
@@ -7926,7 +7962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>45992</v>
       </c>
@@ -7941,7 +7977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>45993</v>
       </c>
@@ -7970,8 +8006,11 @@
       <c r="L6" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="M6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>45994</v>
       </c>
@@ -8000,8 +8039,11 @@
       <c r="L7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="M7">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>45995</v>
       </c>
@@ -8030,8 +8072,11 @@
       <c r="L8">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="M8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>45996</v>
       </c>
@@ -8064,8 +8109,12 @@
         <f>(L7/L8)*100</f>
         <v>14.285714285714285</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9">
+        <f>(M7/M8)*100</f>
+        <v>57.499999999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>45997</v>
       </c>
@@ -8080,7 +8129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>45998</v>
       </c>
@@ -8096,7 +8145,7 @@
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>45999</v>
       </c>
@@ -8114,11 +8163,11 @@
         <v>122</v>
       </c>
       <c r="I12">
-        <f>AVERAGE(I9:L9)</f>
-        <v>9.9402112338999444</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+        <f>AVERAGE(I9:M9)</f>
+        <v>19.452168987119954</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46000</v>
       </c>
@@ -8133,7 +8182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>46001</v>
       </c>
@@ -8148,7 +8197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46002</v>
       </c>
@@ -8163,7 +8212,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>46003</v>
       </c>
@@ -8984,7 +9033,7 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <f t="shared" ref="D70:D123" si="1">SUM(B70:C70)</f>
+        <f t="shared" ref="D70:D133" si="1">SUM(B70:C70)</f>
         <v>4</v>
       </c>
     </row>
@@ -9780,6 +9829,336 @@
       </c>
       <c r="D123">
         <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>2</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>2</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133">
+        <v>3</v>
+      </c>
+      <c r="D133">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+      <c r="D134">
+        <f t="shared" ref="D134:D145" si="2">SUM(B134:C134)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>3</v>
+      </c>
+      <c r="D135">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>2</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>2</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+      <c r="D142">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+      <c r="D145">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -9794,7 +10173,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D661A788-0182-C446-91FA-D86185AF7F82}">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:AF147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -9804,7 +10183,7 @@
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>37</v>
       </c>
@@ -9820,7 +10199,7 @@
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>45989</v>
       </c>
@@ -9843,8 +10222,12 @@
       <c r="H2" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF2" s="1"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>45990</v>
       </c>
@@ -9869,8 +10252,13 @@
         <f>AVERAGE(B95:B124)</f>
         <v>12265.766666666666</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="3">
+        <f>AVERAGE(B126:B147)</f>
+        <v>4398.545454545455</v>
+      </c>
+      <c r="AF3" s="1"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>45991</v>
       </c>
@@ -9881,8 +10269,9 @@
         <v>23611</v>
       </c>
       <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF4" s="1"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>45992</v>
       </c>
@@ -9893,8 +10282,9 @@
         <v>69299</v>
       </c>
       <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF5" s="1"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>45993</v>
       </c>
@@ -9904,12 +10294,13 @@
       <c r="C6" s="8">
         <v>49006</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" t="s">
         <v>124</v>
       </c>
       <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF6" s="1"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>45994</v>
       </c>
@@ -9920,12 +10311,13 @@
         <v>60593</v>
       </c>
       <c r="E7" s="3">
-        <f>SUM(C2:C124)</f>
-        <v>7796142</v>
+        <f>SUM(C2:C147)</f>
+        <v>7924995</v>
       </c>
       <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF7" s="1"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>45995</v>
       </c>
@@ -9936,8 +10328,9 @@
         <v>112498</v>
       </c>
       <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF8" s="1"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>45996</v>
       </c>
@@ -9948,8 +10341,9 @@
         <v>145294</v>
       </c>
       <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF9" s="1"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>45997</v>
       </c>
@@ -9960,8 +10354,9 @@
         <v>78938</v>
       </c>
       <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF10" s="1"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>45998</v>
       </c>
@@ -9972,8 +10367,9 @@
         <v>56748</v>
       </c>
       <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF11" s="1"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>45999</v>
       </c>
@@ -9983,8 +10379,9 @@
       <c r="C12" s="8">
         <v>69137</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF12" s="1"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>46000</v>
       </c>
@@ -9994,8 +10391,9 @@
       <c r="C13" s="8">
         <v>152198</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF13" s="1"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>46001</v>
       </c>
@@ -10005,8 +10403,9 @@
       <c r="C14" s="8">
         <v>85363</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF14" s="1"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>46002</v>
       </c>
@@ -10016,8 +10415,9 @@
       <c r="C15" s="8">
         <v>114782</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="AF15" s="1"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>46003</v>
       </c>
@@ -10027,8 +10427,9 @@
       <c r="C16" s="8">
         <v>214832</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF16" s="1"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>46004</v>
       </c>
@@ -10038,8 +10439,9 @@
       <c r="C17" s="8">
         <v>195632</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF17" s="1"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>46005</v>
       </c>
@@ -10049,8 +10451,9 @@
       <c r="C18" s="8">
         <v>123899</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF18" s="1"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>46006</v>
       </c>
@@ -10060,8 +10463,9 @@
       <c r="C19" s="8">
         <v>146727</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF19" s="1"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>46007</v>
       </c>
@@ -10071,8 +10475,9 @@
       <c r="C20" s="8">
         <v>157910</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF20" s="1"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>46008</v>
       </c>
@@ -10082,8 +10487,9 @@
       <c r="C21" s="8">
         <v>188576</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF21" s="1"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>46009</v>
       </c>
@@ -10093,8 +10499,9 @@
       <c r="C22" s="8">
         <v>162736</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF22" s="1"/>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>46010</v>
       </c>
@@ -10104,8 +10511,9 @@
       <c r="C23" s="8">
         <v>143269</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF23" s="1"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>46011</v>
       </c>
@@ -10115,8 +10523,9 @@
       <c r="C24" s="8">
         <v>151478</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF24" s="1"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>46012</v>
       </c>
@@ -10126,8 +10535,9 @@
       <c r="C25" s="8">
         <v>104644</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF25" s="1"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>46013</v>
       </c>
@@ -10137,8 +10547,9 @@
       <c r="C26" s="8">
         <v>158335</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF26" s="1"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>46014</v>
       </c>
@@ -10148,8 +10559,9 @@
       <c r="C27" s="8">
         <v>157511</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF27" s="1"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>46015</v>
       </c>
@@ -10159,8 +10571,9 @@
       <c r="C28" s="8">
         <v>98678</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF28" s="1"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>46016</v>
       </c>
@@ -10170,8 +10583,9 @@
       <c r="C29" s="8">
         <v>123027</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF29" s="1"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>46017</v>
       </c>
@@ -10181,8 +10595,9 @@
       <c r="C30" s="8">
         <v>125760</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF30" s="1"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>46018</v>
       </c>
@@ -10192,8 +10607,9 @@
       <c r="C31" s="8">
         <v>93906</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF31" s="1"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>46019</v>
       </c>
@@ -10203,8 +10619,9 @@
       <c r="C32" s="8">
         <v>130414</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF32" s="1"/>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>46020</v>
       </c>
@@ -10214,8 +10631,9 @@
       <c r="C33" s="8">
         <v>144820</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF33" s="1"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>46021</v>
       </c>
@@ -10225,8 +10643,9 @@
       <c r="C34" s="8">
         <v>128497</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF34" s="1"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>46022</v>
       </c>
@@ -10236,8 +10655,9 @@
       <c r="C35" s="8">
         <v>103497</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF35" s="1"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>46023</v>
       </c>
@@ -10247,8 +10667,9 @@
       <c r="C36" s="8">
         <v>115365</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF36" s="1"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>46024</v>
       </c>
@@ -10258,8 +10679,9 @@
       <c r="C37" s="8">
         <v>112470</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF37" s="1"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>46025</v>
       </c>
@@ -10269,8 +10691,9 @@
       <c r="C38" s="8">
         <v>87273</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF38" s="1"/>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>46026</v>
       </c>
@@ -10280,8 +10703,9 @@
       <c r="C39" s="8">
         <v>91899</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF39" s="1"/>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>46027</v>
       </c>
@@ -10291,8 +10715,9 @@
       <c r="C40" s="8">
         <v>127081</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF40" s="1"/>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>46028</v>
       </c>
@@ -10302,8 +10727,9 @@
       <c r="C41" s="8">
         <v>118923</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF41" s="1"/>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>46029</v>
       </c>
@@ -10313,8 +10739,9 @@
       <c r="C42" s="8">
         <v>146196</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF42" s="1"/>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>46030</v>
       </c>
@@ -10324,8 +10751,9 @@
       <c r="C43" s="8">
         <v>131943</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF43" s="1"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>46031</v>
       </c>
@@ -10335,8 +10763,9 @@
       <c r="C44" s="8">
         <v>87911</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF44" s="1"/>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>46032</v>
       </c>
@@ -10346,8 +10775,9 @@
       <c r="C45" s="8">
         <v>129350</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF45" s="1"/>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <v>46033</v>
       </c>
@@ -10357,8 +10787,9 @@
       <c r="C46" s="8">
         <v>87163</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF46" s="1"/>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <v>46034</v>
       </c>
@@ -10368,8 +10799,9 @@
       <c r="C47" s="8">
         <v>72633</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF47" s="1"/>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <v>46035</v>
       </c>
@@ -10379,8 +10811,9 @@
       <c r="C48" s="8">
         <v>95455</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF48" s="1"/>
+    </row>
+    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>46036</v>
       </c>
@@ -10390,8 +10823,9 @@
       <c r="C49" s="8">
         <v>117061</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF49" s="1"/>
+    </row>
+    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>46037</v>
       </c>
@@ -10401,8 +10835,9 @@
       <c r="C50" s="8">
         <v>77079</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF50" s="1"/>
+    </row>
+    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>46038</v>
       </c>
@@ -10412,8 +10847,9 @@
       <c r="C51" s="8">
         <v>82669</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF51" s="1"/>
+    </row>
+    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>46039</v>
       </c>
@@ -10423,8 +10859,9 @@
       <c r="C52" s="8">
         <v>74776</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF52" s="1"/>
+    </row>
+    <row r="53" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>46040</v>
       </c>
@@ -10434,8 +10871,9 @@
       <c r="C53" s="8">
         <v>90533</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF53" s="1"/>
+    </row>
+    <row r="54" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>46041</v>
       </c>
@@ -10445,8 +10883,9 @@
       <c r="C54" s="8">
         <v>64761</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF54" s="1"/>
+    </row>
+    <row r="55" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>46042</v>
       </c>
@@ -10456,8 +10895,9 @@
       <c r="C55" s="8">
         <v>70712</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF55" s="1"/>
+    </row>
+    <row r="56" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>46043</v>
       </c>
@@ -10467,8 +10907,9 @@
       <c r="C56" s="8">
         <v>91045</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF56" s="1"/>
+    </row>
+    <row r="57" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>46044</v>
       </c>
@@ -10478,8 +10919,9 @@
       <c r="C57" s="8">
         <v>122687</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF57" s="1"/>
+    </row>
+    <row r="58" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>46045</v>
       </c>
@@ -10489,8 +10931,9 @@
       <c r="C58" s="8">
         <v>55661</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF58" s="1"/>
+    </row>
+    <row r="59" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>46046</v>
       </c>
@@ -10500,8 +10943,9 @@
       <c r="C59" s="8">
         <v>69876</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF59" s="1"/>
+    </row>
+    <row r="60" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>46047</v>
       </c>
@@ -10511,8 +10955,9 @@
       <c r="C60" s="8">
         <v>51679</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF60" s="1"/>
+    </row>
+    <row r="61" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>46048</v>
       </c>
@@ -10522,8 +10967,9 @@
       <c r="C61" s="8">
         <v>49703</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF61" s="1"/>
+    </row>
+    <row r="62" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>46049</v>
       </c>
@@ -10533,8 +10979,9 @@
       <c r="C62" s="8">
         <v>40681</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF62" s="1"/>
+    </row>
+    <row r="63" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>46050</v>
       </c>
@@ -10544,8 +10991,9 @@
       <c r="C63" s="8">
         <v>94663</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF63" s="1"/>
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>46051</v>
       </c>
@@ -10555,8 +11003,9 @@
       <c r="C64" s="8">
         <v>48741</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF64" s="1"/>
+    </row>
+    <row r="65" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>46052</v>
       </c>
@@ -10566,8 +11015,9 @@
       <c r="C65" s="8">
         <v>27903</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF65" s="1"/>
+    </row>
+    <row r="66" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>46053</v>
       </c>
@@ -10577,8 +11027,9 @@
       <c r="C66" s="8">
         <v>70805</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF66" s="1"/>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>46054</v>
       </c>
@@ -10588,8 +11039,9 @@
       <c r="C67" s="8">
         <v>42561</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF67" s="1"/>
+    </row>
+    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>46055</v>
       </c>
@@ -10599,8 +11051,9 @@
       <c r="C68" s="8">
         <v>34732</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF68" s="1"/>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>46056</v>
       </c>
@@ -10610,8 +11063,9 @@
       <c r="C69" s="8">
         <v>101341</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF69" s="1"/>
+    </row>
+    <row r="70" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>46057</v>
       </c>
@@ -10621,8 +11075,9 @@
       <c r="C70" s="8">
         <v>50960</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF70" s="1"/>
+    </row>
+    <row r="71" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>46058</v>
       </c>
@@ -10632,8 +11087,9 @@
       <c r="C71" s="8">
         <v>67043</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF71" s="1"/>
+    </row>
+    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>46059</v>
       </c>
@@ -10643,8 +11099,9 @@
       <c r="C72" s="8">
         <v>74932</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF72" s="1"/>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>46060</v>
       </c>
@@ -10654,8 +11111,9 @@
       <c r="C73" s="8">
         <v>36460</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF73" s="1"/>
+    </row>
+    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <v>46061</v>
       </c>
@@ -10665,8 +11123,9 @@
       <c r="C74" s="8">
         <v>12204</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF74" s="1"/>
+    </row>
+    <row r="75" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>46062</v>
       </c>
@@ -10676,8 +11135,9 @@
       <c r="C75" s="8">
         <v>10186</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF75" s="1"/>
+    </row>
+    <row r="76" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>46063</v>
       </c>
@@ -10687,8 +11147,9 @@
       <c r="C76" s="8">
         <v>21000</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF76" s="1"/>
+    </row>
+    <row r="77" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>46064</v>
       </c>
@@ -10698,8 +11159,9 @@
       <c r="C77" s="8">
         <v>50204</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF77" s="1"/>
+    </row>
+    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>46065</v>
       </c>
@@ -10709,8 +11171,9 @@
       <c r="C78" s="8">
         <v>19383</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF78" s="1"/>
+    </row>
+    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>46066</v>
       </c>
@@ -10720,8 +11183,9 @@
       <c r="C79" s="8">
         <v>15880</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF79" s="1"/>
+    </row>
+    <row r="80" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>46067</v>
       </c>
@@ -10731,8 +11195,9 @@
       <c r="C80" s="8">
         <v>49916</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF80" s="1"/>
+    </row>
+    <row r="81" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <v>46068</v>
       </c>
@@ -10742,8 +11207,9 @@
       <c r="C81" s="8">
         <v>18125</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF81" s="1"/>
+    </row>
+    <row r="82" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <v>46069</v>
       </c>
@@ -10753,8 +11219,9 @@
       <c r="C82" s="8">
         <v>2448</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF82" s="1"/>
+    </row>
+    <row r="83" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <v>46070</v>
       </c>
@@ -10764,8 +11231,9 @@
       <c r="C83" s="8">
         <v>32959</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF83" s="1"/>
+    </row>
+    <row r="84" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>46071</v>
       </c>
@@ -10775,8 +11243,9 @@
       <c r="C84" s="8">
         <v>6177</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF84" s="1"/>
+    </row>
+    <row r="85" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>46072</v>
       </c>
@@ -10786,8 +11255,9 @@
       <c r="C85" s="8">
         <v>17316</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF85" s="1"/>
+    </row>
+    <row r="86" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>46073</v>
       </c>
@@ -10797,8 +11267,9 @@
       <c r="C86" s="8">
         <v>2976</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF86" s="1"/>
+    </row>
+    <row r="87" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <v>46074</v>
       </c>
@@ -10808,8 +11279,9 @@
       <c r="C87" s="8">
         <v>26099</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF87" s="1"/>
+    </row>
+    <row r="88" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <v>46075</v>
       </c>
@@ -10819,8 +11291,9 @@
       <c r="C88" s="8">
         <v>17702</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF88" s="1"/>
+    </row>
+    <row r="89" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <v>46076</v>
       </c>
@@ -10830,8 +11303,9 @@
       <c r="C89" s="8">
         <v>30698</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF89" s="1"/>
+    </row>
+    <row r="90" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <v>46077</v>
       </c>
@@ -10841,8 +11315,9 @@
       <c r="C90" s="8">
         <v>8495</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF90" s="1"/>
+    </row>
+    <row r="91" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <v>46078</v>
       </c>
@@ -10852,8 +11327,9 @@
       <c r="C91" s="8">
         <v>3285</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF91" s="1"/>
+    </row>
+    <row r="92" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <v>46079</v>
       </c>
@@ -10863,8 +11339,9 @@
       <c r="C92" s="8">
         <v>15993</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF92" s="1"/>
+    </row>
+    <row r="93" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <v>46080</v>
       </c>
@@ -10874,8 +11351,9 @@
       <c r="C93" s="8">
         <v>4513</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF93" s="1"/>
+    </row>
+    <row r="94" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <v>46081</v>
       </c>
@@ -10885,8 +11363,9 @@
       <c r="C94" s="8">
         <v>38031</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF94" s="1"/>
+    </row>
+    <row r="95" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <v>46082</v>
       </c>
@@ -10896,8 +11375,9 @@
       <c r="C95" s="8">
         <v>34463</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF95" s="1"/>
+    </row>
+    <row r="96" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>46083</v>
       </c>
@@ -10907,8 +11387,9 @@
       <c r="C96" s="3">
         <v>1936</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF96" s="1"/>
+    </row>
+    <row r="97" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>46084</v>
       </c>
@@ -10918,8 +11399,9 @@
       <c r="C97" s="3">
         <v>7014</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF97" s="1"/>
+    </row>
+    <row r="98" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>46085</v>
       </c>
@@ -10929,8 +11411,9 @@
       <c r="C98" s="3">
         <v>38238</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF98" s="1"/>
+    </row>
+    <row r="99" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>46086</v>
       </c>
@@ -10940,8 +11423,9 @@
       <c r="C99" s="3">
         <v>30204</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF99" s="1"/>
+    </row>
+    <row r="100" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>46087</v>
       </c>
@@ -10951,8 +11435,9 @@
       <c r="C100" s="3">
         <v>9135</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF100" s="1"/>
+    </row>
+    <row r="101" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>46088</v>
       </c>
@@ -10962,8 +11447,9 @@
       <c r="C101" s="3">
         <v>53306</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF101" s="1"/>
+    </row>
+    <row r="102" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>46089</v>
       </c>
@@ -10973,8 +11459,9 @@
       <c r="C102" s="3">
         <v>10527</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF102" s="1"/>
+    </row>
+    <row r="103" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>46090</v>
       </c>
@@ -10984,8 +11471,9 @@
       <c r="C103" s="3">
         <v>3035</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF103" s="1"/>
+    </row>
+    <row r="104" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>46091</v>
       </c>
@@ -10995,8 +11483,9 @@
       <c r="C104" s="3">
         <v>4325</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF104" s="1"/>
+    </row>
+    <row r="105" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>46092</v>
       </c>
@@ -11006,8 +11495,9 @@
       <c r="C105" s="3">
         <v>28858</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF105" s="1"/>
+    </row>
+    <row r="106" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>46093</v>
       </c>
@@ -11017,8 +11507,9 @@
       <c r="C106" s="3">
         <v>3149</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF106" s="1"/>
+    </row>
+    <row r="107" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>46094</v>
       </c>
@@ -11028,8 +11519,9 @@
       <c r="C107" s="3">
         <v>9932</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF107" s="1"/>
+    </row>
+    <row r="108" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>46095</v>
       </c>
@@ -11039,8 +11531,9 @@
       <c r="C108" s="3">
         <v>5596</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF108" s="1"/>
+    </row>
+    <row r="109" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>46096</v>
       </c>
@@ -11050,8 +11543,9 @@
       <c r="C109" s="3">
         <v>4241</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF109" s="1"/>
+    </row>
+    <row r="110" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>46097</v>
       </c>
@@ -11061,8 +11555,9 @@
       <c r="C110" s="3">
         <v>4599</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF110" s="1"/>
+    </row>
+    <row r="111" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>46098</v>
       </c>
@@ -11072,8 +11567,9 @@
       <c r="C111" s="3">
         <v>3752</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF111" s="1"/>
+    </row>
+    <row r="112" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>46099</v>
       </c>
@@ -11083,8 +11579,9 @@
       <c r="C112" s="3">
         <v>21412</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF112" s="1"/>
+    </row>
+    <row r="113" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>46100</v>
       </c>
@@ -11094,8 +11591,9 @@
       <c r="C113" s="3">
         <v>14166</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF113" s="1"/>
+    </row>
+    <row r="114" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>46101</v>
       </c>
@@ -11105,8 +11603,9 @@
       <c r="C114" s="3">
         <v>7818</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF114" s="1"/>
+    </row>
+    <row r="115" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>46102</v>
       </c>
@@ -11116,8 +11615,9 @@
       <c r="C115" s="3">
         <v>4135</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF115" s="1"/>
+    </row>
+    <row r="116" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>46103</v>
       </c>
@@ -11127,8 +11627,9 @@
       <c r="C116" s="3">
         <v>2868</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF116" s="1"/>
+    </row>
+    <row r="117" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>46104</v>
       </c>
@@ -11138,8 +11639,9 @@
       <c r="C117" s="3">
         <v>12377</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF117" s="1"/>
+    </row>
+    <row r="118" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>46105</v>
       </c>
@@ -11149,8 +11651,9 @@
       <c r="C118" s="3">
         <v>5396</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF118" s="1"/>
+    </row>
+    <row r="119" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>46106</v>
       </c>
@@ -11160,8 +11663,9 @@
       <c r="C119" s="3">
         <v>7096</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF119" s="1"/>
+    </row>
+    <row r="120" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>46107</v>
       </c>
@@ -11171,8 +11675,9 @@
       <c r="C120" s="3">
         <v>8392</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF120" s="1"/>
+    </row>
+    <row r="121" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>46108</v>
       </c>
@@ -11182,8 +11687,9 @@
       <c r="C121" s="3">
         <v>7505</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF121" s="1"/>
+    </row>
+    <row r="122" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>46109</v>
       </c>
@@ -11193,8 +11699,9 @@
       <c r="C122" s="3">
         <v>16607</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF122" s="1"/>
+    </row>
+    <row r="123" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>46110</v>
       </c>
@@ -11204,8 +11711,9 @@
       <c r="C123" s="3">
         <v>3726</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="AF123" s="1"/>
+    </row>
+    <row r="124" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>46111</v>
       </c>
@@ -11215,6 +11723,283 @@
       <c r="C124" s="3">
         <v>4165</v>
       </c>
+      <c r="AF124" s="1"/>
+    </row>
+    <row r="125" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B125" s="12">
+        <v>32085</v>
+      </c>
+      <c r="C125" s="3">
+        <v>32085</v>
+      </c>
+      <c r="AF125" s="1"/>
+    </row>
+    <row r="126" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B126" s="12">
+        <v>4714</v>
+      </c>
+      <c r="C126" s="3">
+        <v>4714</v>
+      </c>
+      <c r="AF126" s="1"/>
+    </row>
+    <row r="127" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B127" s="12">
+        <v>3713</v>
+      </c>
+      <c r="C127" s="3">
+        <v>3713</v>
+      </c>
+      <c r="AF127" s="1"/>
+    </row>
+    <row r="128" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B128" s="12">
+        <v>3392</v>
+      </c>
+      <c r="C128" s="3">
+        <v>3392</v>
+      </c>
+      <c r="AF128" s="1"/>
+    </row>
+    <row r="129" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B129" s="12">
+        <v>12676</v>
+      </c>
+      <c r="C129" s="3">
+        <v>12676</v>
+      </c>
+      <c r="AF129" s="1"/>
+    </row>
+    <row r="130" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B130" s="12">
+        <v>3604</v>
+      </c>
+      <c r="C130" s="3">
+        <v>3604</v>
+      </c>
+      <c r="AF130" s="1"/>
+    </row>
+    <row r="131" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B131" s="12">
+        <v>3598</v>
+      </c>
+      <c r="C131" s="3">
+        <v>3598</v>
+      </c>
+      <c r="AF131" s="1"/>
+    </row>
+    <row r="132" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B132" s="12">
+        <v>2501</v>
+      </c>
+      <c r="C132" s="3">
+        <v>2501</v>
+      </c>
+      <c r="AF132" s="1"/>
+    </row>
+    <row r="133" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B133" s="12">
+        <v>9247</v>
+      </c>
+      <c r="C133" s="3">
+        <v>9247</v>
+      </c>
+      <c r="AF133" s="1"/>
+    </row>
+    <row r="134" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B134" s="12">
+        <v>3532</v>
+      </c>
+      <c r="C134" s="3">
+        <v>3532</v>
+      </c>
+      <c r="AF134" s="1"/>
+    </row>
+    <row r="135" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B135" s="12">
+        <v>8987</v>
+      </c>
+      <c r="C135" s="3">
+        <v>8987</v>
+      </c>
+      <c r="AF135" s="1"/>
+    </row>
+    <row r="136" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B136" s="12">
+        <v>3590</v>
+      </c>
+      <c r="C136" s="3">
+        <v>3590</v>
+      </c>
+      <c r="AF136" s="1"/>
+    </row>
+    <row r="137" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B137" s="12">
+        <v>3714</v>
+      </c>
+      <c r="C137" s="3">
+        <v>3714</v>
+      </c>
+      <c r="AF137" s="1"/>
+    </row>
+    <row r="138" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B138" s="12">
+        <v>2767</v>
+      </c>
+      <c r="C138" s="3">
+        <v>2767</v>
+      </c>
+      <c r="AF138" s="1"/>
+    </row>
+    <row r="139" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B139" s="12">
+        <v>3622</v>
+      </c>
+      <c r="C139" s="3">
+        <v>3622</v>
+      </c>
+      <c r="AF139" s="1"/>
+    </row>
+    <row r="140" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B140" s="12">
+        <v>3136</v>
+      </c>
+      <c r="C140" s="3">
+        <v>3136</v>
+      </c>
+      <c r="AF140" s="1"/>
+    </row>
+    <row r="141" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B141" s="12">
+        <v>2753</v>
+      </c>
+      <c r="C141" s="3">
+        <v>2753</v>
+      </c>
+      <c r="AF141" s="1"/>
+    </row>
+    <row r="142" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B142" s="12">
+        <v>3271</v>
+      </c>
+      <c r="C142" s="3">
+        <v>3271</v>
+      </c>
+      <c r="AF142" s="1"/>
+    </row>
+    <row r="143" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B143" s="12">
+        <v>3556</v>
+      </c>
+      <c r="C143" s="3">
+        <v>3556</v>
+      </c>
+      <c r="AF143" s="1"/>
+    </row>
+    <row r="144" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B144" s="12">
+        <v>4673</v>
+      </c>
+      <c r="C144" s="3">
+        <v>4673</v>
+      </c>
+      <c r="AF144" s="1"/>
+    </row>
+    <row r="145" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B145" s="12">
+        <v>3561</v>
+      </c>
+      <c r="C145" s="3">
+        <v>3561</v>
+      </c>
+      <c r="AF145" s="1"/>
+    </row>
+    <row r="146" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B146" s="12">
+        <v>2857</v>
+      </c>
+      <c r="C146" s="3">
+        <v>2857</v>
+      </c>
+      <c r="AF146" s="1"/>
+    </row>
+    <row r="147" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B147" s="12">
+        <v>3304</v>
+      </c>
+      <c r="C147" s="3">
+        <v>3304</v>
+      </c>
+      <c r="AF147" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11228,19 +12013,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1556A1A1-ED11-3146-B060-85C0AF0DE640}">
-  <dimension ref="A1:M124"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.83203125" style="9"/>
     <col min="3" max="4" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>42</v>
@@ -11255,16 +12040,16 @@
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>45989</v>
       </c>
       <c r="B2" s="9">
-        <f>ROUNDUP(C2, 0)</f>
+        <f>ROUNDUP(C2,0)</f>
         <v>23</v>
       </c>
       <c r="C2" s="3">
-        <v>22.092099999999999</v>
+        <v>22.09</v>
       </c>
       <c r="D2" s="8">
         <v>1326</v>
@@ -11283,17 +12068,20 @@
       <c r="J2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>45990</v>
       </c>
       <c r="B3" s="9">
-        <f>ROUNDUP(C3, 0)</f>
+        <f t="shared" ref="B3:B66" si="0">ROUNDUP(C3,0)</f>
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>15.119199999999999</v>
+        <v>15.12</v>
       </c>
       <c r="D3" s="8">
         <v>907</v>
@@ -11304,7 +12092,7 @@
       </c>
       <c r="H3" s="9">
         <f>AVERAGE(C35:C65)</f>
-        <v>86.739064516128991</v>
+        <v>86.739354838709673</v>
       </c>
       <c r="I3" s="9">
         <f>AVERAGE(B67:B94)</f>
@@ -11314,33 +12102,37 @@
         <f>AVERAGE(B95:B124)</f>
         <v>14.933333333333334</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3" s="9">
+        <f>AVERAGE(B126:B147)</f>
+        <v>4.9090909090909092</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>45991</v>
       </c>
       <c r="B4" s="9">
-        <f>ROUNDUP(C4, 0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>19.8142</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="D4" s="8">
         <v>1188</v>
       </c>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>45992</v>
       </c>
       <c r="B5" s="9">
-        <f t="shared" ref="B5:B67" si="0">ROUNDUP(C5, 0)</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="C5" s="3">
-        <v>62.1937</v>
+        <v>62.19</v>
       </c>
       <c r="D5" s="8">
         <v>3731</v>
@@ -11350,7 +12142,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>45993</v>
       </c>
@@ -11359,18 +12151,18 @@
         <v>58</v>
       </c>
       <c r="C6" s="3">
-        <v>57.237099999999899</v>
+        <v>57.24</v>
       </c>
       <c r="D6" s="8">
         <v>3435</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="9">
-        <f>SUM(C2:C124)</f>
-        <v>7875.5110999999924</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <f>SUM(C2:C147)</f>
+        <v>8000.7899999999981</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>45994</v>
       </c>
@@ -11379,7 +12171,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="3">
-        <v>72.176400000000001</v>
+        <v>72.180000000000007</v>
       </c>
       <c r="D7" s="8">
         <v>4329</v>
@@ -11387,7 +12179,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>45995</v>
       </c>
@@ -11396,14 +12188,14 @@
         <v>104</v>
       </c>
       <c r="C8" s="3">
-        <v>103.3441</v>
+        <v>103.34</v>
       </c>
       <c r="D8" s="8">
         <v>6201</v>
       </c>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>45996</v>
       </c>
@@ -11412,14 +12204,14 @@
         <v>151</v>
       </c>
       <c r="C9" s="3">
-        <v>150.15520000000001</v>
+        <v>150.16</v>
       </c>
       <c r="D9" s="8">
         <v>9011</v>
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>45997</v>
       </c>
@@ -11428,14 +12220,14 @@
         <v>77</v>
       </c>
       <c r="C10" s="3">
-        <v>76.3035</v>
+        <v>76.3</v>
       </c>
       <c r="D10" s="8">
         <v>4575</v>
       </c>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>45998</v>
       </c>
@@ -11444,14 +12236,14 @@
         <v>54</v>
       </c>
       <c r="C11" s="3">
-        <v>53.886799999999901</v>
+        <v>53.89</v>
       </c>
       <c r="D11" s="8">
         <v>3234</v>
       </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>45999</v>
       </c>
@@ -11460,14 +12252,14 @@
         <v>72</v>
       </c>
       <c r="C12" s="3">
-        <v>71.2898</v>
+        <v>71.290000000000006</v>
       </c>
       <c r="D12" s="8">
         <v>4278</v>
       </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>46000</v>
       </c>
@@ -11476,14 +12268,14 @@
         <v>141</v>
       </c>
       <c r="C13" s="3">
-        <v>140.8578</v>
+        <v>140.86000000000001</v>
       </c>
       <c r="D13" s="8">
         <v>8453</v>
       </c>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>46001</v>
       </c>
@@ -11492,14 +12284,14 @@
         <v>127</v>
       </c>
       <c r="C14" s="3">
-        <v>126.508799999999</v>
+        <v>126.51</v>
       </c>
       <c r="D14" s="8">
         <v>7594</v>
       </c>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>46002</v>
       </c>
@@ -11508,14 +12300,14 @@
         <v>114</v>
       </c>
       <c r="C15" s="3">
-        <v>113.372799999999</v>
+        <v>113.37</v>
       </c>
       <c r="D15" s="8">
         <v>6802</v>
       </c>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>46003</v>
       </c>
@@ -11524,7 +12316,7 @@
         <v>183</v>
       </c>
       <c r="C16" s="3">
-        <v>182.87780000000001</v>
+        <v>182.88</v>
       </c>
       <c r="D16" s="8">
         <v>10970</v>
@@ -11540,7 +12332,7 @@
         <v>183</v>
       </c>
       <c r="C17" s="3">
-        <v>182.61089999999999</v>
+        <v>182.61</v>
       </c>
       <c r="D17" s="8">
         <v>10957</v>
@@ -11556,7 +12348,7 @@
         <v>110</v>
       </c>
       <c r="C18" s="3">
-        <v>109.337199999999</v>
+        <v>109.34</v>
       </c>
       <c r="D18" s="8">
         <v>6559</v>
@@ -11572,7 +12364,7 @@
         <v>144</v>
       </c>
       <c r="C19" s="3">
-        <v>143.18169999999901</v>
+        <v>143.18</v>
       </c>
       <c r="D19" s="8">
         <v>8593</v>
@@ -11588,7 +12380,7 @@
         <v>141</v>
       </c>
       <c r="C20" s="3">
-        <v>140.89709999999999</v>
+        <v>140.9</v>
       </c>
       <c r="D20" s="8">
         <v>8457</v>
@@ -11604,7 +12396,7 @@
         <v>174</v>
       </c>
       <c r="C21" s="3">
-        <v>173.5873</v>
+        <v>173.59</v>
       </c>
       <c r="D21" s="8">
         <v>10415</v>
@@ -11620,7 +12412,7 @@
         <v>156</v>
       </c>
       <c r="C22" s="3">
-        <v>155.47259999999901</v>
+        <v>155.47</v>
       </c>
       <c r="D22" s="8">
         <v>9331</v>
@@ -11636,7 +12428,7 @@
         <v>151</v>
       </c>
       <c r="C23" s="3">
-        <v>150.10239999999899</v>
+        <v>150.1</v>
       </c>
       <c r="D23" s="8">
         <v>9006</v>
@@ -11652,7 +12444,7 @@
         <v>162</v>
       </c>
       <c r="C24" s="3">
-        <v>161.82650000000001</v>
+        <v>161.83000000000001</v>
       </c>
       <c r="D24" s="8">
         <v>9711</v>
@@ -11668,7 +12460,7 @@
         <v>98</v>
       </c>
       <c r="C25" s="3">
-        <v>97.768500000000003</v>
+        <v>97.77</v>
       </c>
       <c r="D25" s="8">
         <v>5864</v>
@@ -11684,7 +12476,7 @@
         <v>156</v>
       </c>
       <c r="C26" s="3">
-        <v>155.7183</v>
+        <v>155.72</v>
       </c>
       <c r="D26" s="8">
         <v>9344</v>
@@ -11700,7 +12492,7 @@
         <v>165</v>
       </c>
       <c r="C27" s="3">
-        <v>164.42329999999899</v>
+        <v>164.42</v>
       </c>
       <c r="D27" s="8">
         <v>9866</v>
@@ -11716,7 +12508,7 @@
         <v>105</v>
       </c>
       <c r="C28" s="3">
-        <v>104.7624</v>
+        <v>104.76</v>
       </c>
       <c r="D28" s="8">
         <v>6284</v>
@@ -11732,7 +12524,7 @@
         <v>129</v>
       </c>
       <c r="C29" s="3">
-        <v>128.89439999999999</v>
+        <v>128.88999999999999</v>
       </c>
       <c r="D29" s="8">
         <v>7735</v>
@@ -11748,7 +12540,7 @@
         <v>131</v>
       </c>
       <c r="C30" s="3">
-        <v>130.7637</v>
+        <v>130.76</v>
       </c>
       <c r="D30" s="8">
         <v>7845</v>
@@ -11765,7 +12557,7 @@
         <v>93</v>
       </c>
       <c r="C31" s="3">
-        <v>92.820099999999996</v>
+        <v>92.82</v>
       </c>
       <c r="D31" s="8">
         <v>5571</v>
@@ -11782,7 +12574,7 @@
         <v>144</v>
       </c>
       <c r="C32" s="3">
-        <v>143.98849999999999</v>
+        <v>143.99</v>
       </c>
       <c r="D32" s="8">
         <v>8638</v>
@@ -11799,7 +12591,7 @@
         <v>138</v>
       </c>
       <c r="C33" s="3">
-        <v>137.218299999999</v>
+        <v>137.22</v>
       </c>
       <c r="D33" s="8">
         <v>8234</v>
@@ -11816,7 +12608,7 @@
         <v>132</v>
       </c>
       <c r="C34" s="3">
-        <v>131.336199999999</v>
+        <v>131.34</v>
       </c>
       <c r="D34" s="8">
         <v>7879</v>
@@ -11833,7 +12625,7 @@
         <v>109</v>
       </c>
       <c r="C35" s="3">
-        <v>108.71850000000001</v>
+        <v>108.72</v>
       </c>
       <c r="D35" s="8">
         <v>6524</v>
@@ -11850,7 +12642,7 @@
         <v>106</v>
       </c>
       <c r="C36" s="3">
-        <v>105.8099</v>
+        <v>105.81</v>
       </c>
       <c r="D36" s="8">
         <v>6350</v>
@@ -11867,7 +12659,7 @@
         <v>151</v>
       </c>
       <c r="C37" s="3">
-        <v>150.00550000000001</v>
+        <v>150.01</v>
       </c>
       <c r="D37" s="8">
         <v>9001</v>
@@ -11884,7 +12676,7 @@
         <v>76</v>
       </c>
       <c r="C38" s="3">
-        <v>75.280599999999893</v>
+        <v>75.28</v>
       </c>
       <c r="D38" s="8">
         <v>4515</v>
@@ -11901,7 +12693,7 @@
         <v>90</v>
       </c>
       <c r="C39" s="3">
-        <v>89.936799999999906</v>
+        <v>89.94</v>
       </c>
       <c r="D39" s="8">
         <v>5399</v>
@@ -11917,7 +12709,7 @@
         <v>121</v>
       </c>
       <c r="C40" s="3">
-        <v>120.0656</v>
+        <v>120.07</v>
       </c>
       <c r="D40" s="8">
         <v>7203</v>
@@ -11933,7 +12725,7 @@
         <v>110</v>
       </c>
       <c r="C41" s="3">
-        <v>109.74379999999999</v>
+        <v>109.74</v>
       </c>
       <c r="D41" s="8">
         <v>6585</v>
@@ -11949,7 +12741,7 @@
         <v>149</v>
       </c>
       <c r="C42" s="3">
-        <v>148.58769999999899</v>
+        <v>148.59</v>
       </c>
       <c r="D42" s="8">
         <v>8917</v>
@@ -11965,7 +12757,7 @@
         <v>148</v>
       </c>
       <c r="C43" s="3">
-        <v>147.83600000000001</v>
+        <v>147.84</v>
       </c>
       <c r="D43" s="8">
         <v>8869</v>
@@ -11981,7 +12773,7 @@
         <v>122</v>
       </c>
       <c r="C44" s="3">
-        <v>121.65179999999999</v>
+        <v>121.65</v>
       </c>
       <c r="D44" s="8">
         <v>7299</v>
@@ -11997,7 +12789,7 @@
         <v>116</v>
       </c>
       <c r="C45" s="3">
-        <v>115.4661</v>
+        <v>115.47</v>
       </c>
       <c r="D45" s="8">
         <v>6928</v>
@@ -12013,7 +12805,7 @@
         <v>74</v>
       </c>
       <c r="C46" s="3">
-        <v>73.106499999999997</v>
+        <v>73.11</v>
       </c>
       <c r="D46" s="8">
         <v>4383</v>
@@ -12029,7 +12821,7 @@
         <v>73</v>
       </c>
       <c r="C47" s="3">
-        <v>72.736199999999897</v>
+        <v>72.739999999999995</v>
       </c>
       <c r="D47" s="8">
         <v>4363</v>
@@ -12045,7 +12837,7 @@
         <v>83</v>
       </c>
       <c r="C48" s="3">
-        <v>82.632099999999994</v>
+        <v>82.63</v>
       </c>
       <c r="D48" s="8">
         <v>4956</v>
@@ -12061,7 +12853,7 @@
         <v>117</v>
       </c>
       <c r="C49" s="3">
-        <v>116.2405</v>
+        <v>116.24</v>
       </c>
       <c r="D49" s="8">
         <v>6974</v>
@@ -12077,7 +12869,7 @@
         <v>76</v>
       </c>
       <c r="C50" s="3">
-        <v>75.569400000000002</v>
+        <v>75.569999999999993</v>
       </c>
       <c r="D50" s="8">
         <v>4531</v>
@@ -12093,7 +12885,7 @@
         <v>75</v>
       </c>
       <c r="C51" s="3">
-        <v>74.689899999999994</v>
+        <v>74.69</v>
       </c>
       <c r="D51" s="8">
         <v>4482</v>
@@ -12109,7 +12901,7 @@
         <v>64</v>
       </c>
       <c r="C52" s="3">
-        <v>63.148000000000003</v>
+        <v>63.15</v>
       </c>
       <c r="D52" s="8">
         <v>3788</v>
@@ -12125,7 +12917,7 @@
         <v>76</v>
       </c>
       <c r="C53" s="3">
-        <v>75.619500000000002</v>
+        <v>75.62</v>
       </c>
       <c r="D53" s="8">
         <v>4539</v>
@@ -12141,7 +12933,7 @@
         <v>89</v>
       </c>
       <c r="C54" s="3">
-        <v>88.530199999999994</v>
+        <v>88.53</v>
       </c>
       <c r="D54" s="8">
         <v>5309</v>
@@ -12157,7 +12949,7 @@
         <v>60</v>
       </c>
       <c r="C55" s="3">
-        <v>59.229300000000002</v>
+        <v>59.23</v>
       </c>
       <c r="D55" s="8">
         <v>3555</v>
@@ -12173,7 +12965,7 @@
         <v>87</v>
       </c>
       <c r="C56" s="3">
-        <v>86.1768</v>
+        <v>86.18</v>
       </c>
       <c r="D56" s="8">
         <v>5171</v>
@@ -12189,7 +12981,7 @@
         <v>115</v>
       </c>
       <c r="C57" s="3">
-        <v>114.0307</v>
+        <v>114.03</v>
       </c>
       <c r="D57" s="8">
         <v>6842</v>
@@ -12205,7 +12997,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="3">
-        <v>56.0334</v>
+        <v>56.03</v>
       </c>
       <c r="D58" s="8">
         <v>3363</v>
@@ -12221,7 +13013,7 @@
         <v>60</v>
       </c>
       <c r="C59" s="3">
-        <v>59.493699999999997</v>
+        <v>59.49</v>
       </c>
       <c r="D59" s="8">
         <v>3571</v>
@@ -12237,7 +13029,7 @@
         <v>79</v>
       </c>
       <c r="C60" s="3">
-        <v>78.174499999999995</v>
+        <v>78.17</v>
       </c>
       <c r="D60" s="8">
         <v>4692</v>
@@ -12253,7 +13045,7 @@
         <v>40</v>
       </c>
       <c r="C61" s="3">
-        <v>39.068499999999901</v>
+        <v>39.07</v>
       </c>
       <c r="D61" s="8">
         <v>2345</v>
@@ -12269,7 +13061,7 @@
         <v>39</v>
       </c>
       <c r="C62" s="3">
-        <v>38.460099999999997</v>
+        <v>38.46</v>
       </c>
       <c r="D62" s="8">
         <v>2310</v>
@@ -12285,7 +13077,7 @@
         <v>79</v>
       </c>
       <c r="C63" s="3">
-        <v>78.484699999999904</v>
+        <v>78.48</v>
       </c>
       <c r="D63" s="8">
         <v>4708</v>
@@ -12301,7 +13093,7 @@
         <v>41</v>
       </c>
       <c r="C64" s="3">
-        <v>40.751399999999897</v>
+        <v>40.75</v>
       </c>
       <c r="D64" s="8">
         <v>2443</v>
@@ -12317,7 +13109,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="3">
-        <v>23.633299999999998</v>
+        <v>23.63</v>
       </c>
       <c r="D65" s="8">
         <v>1417</v>
@@ -12333,7 +13125,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="3">
-        <v>102.337499999999</v>
+        <v>102.34</v>
       </c>
       <c r="D66" s="8">
         <v>6139</v>
@@ -12345,11 +13137,11 @@
         <v>46054</v>
       </c>
       <c r="B67" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B67:B130" si="1">ROUNDUP(C67,0)</f>
         <v>36</v>
       </c>
       <c r="C67" s="3">
-        <v>35.338299999999997</v>
+        <v>35.340000000000003</v>
       </c>
       <c r="D67" s="8">
         <v>2119</v>
@@ -12361,11 +13153,11 @@
         <v>46055</v>
       </c>
       <c r="B68" s="9">
-        <f t="shared" ref="B68:B124" si="1">ROUNDUP(C68, 0)</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="C68" s="3">
-        <v>85.838999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D68" s="8">
         <v>5151</v>
@@ -12381,7 +13173,7 @@
         <v>90</v>
       </c>
       <c r="C69" s="3">
-        <v>89.372600000000006</v>
+        <v>89.37</v>
       </c>
       <c r="D69" s="8">
         <v>5363</v>
@@ -12397,7 +13189,7 @@
         <v>60</v>
       </c>
       <c r="C70" s="3">
-        <v>59.313999999999901</v>
+        <v>59.31</v>
       </c>
       <c r="D70" s="8">
         <v>3559</v>
@@ -12413,7 +13205,7 @@
         <v>86</v>
       </c>
       <c r="C71" s="3">
-        <v>85.885099999999994</v>
+        <v>85.89</v>
       </c>
       <c r="D71" s="8">
         <v>5155</v>
@@ -12429,7 +13221,7 @@
         <v>78</v>
       </c>
       <c r="C72" s="3">
-        <v>77.071200000000005</v>
+        <v>77.069999999999993</v>
       </c>
       <c r="D72" s="8">
         <v>4624</v>
@@ -12445,7 +13237,7 @@
         <v>40</v>
       </c>
       <c r="C73" s="3">
-        <v>39.328299999999999</v>
+        <v>39.33</v>
       </c>
       <c r="D73" s="8">
         <v>2358</v>
@@ -12461,7 +13253,7 @@
         <v>17</v>
       </c>
       <c r="C74" s="3">
-        <v>16.212799999999898</v>
+        <v>16.21</v>
       </c>
       <c r="D74" s="8">
         <v>974</v>
@@ -12477,7 +13269,7 @@
         <v>11</v>
       </c>
       <c r="C75" s="3">
-        <v>10.7166</v>
+        <v>10.72</v>
       </c>
       <c r="D75" s="8">
         <v>644</v>
@@ -12493,7 +13285,7 @@
         <v>18</v>
       </c>
       <c r="C76" s="3">
-        <v>17.838200000000001</v>
+        <v>17.84</v>
       </c>
       <c r="D76" s="8">
         <v>1071</v>
@@ -12509,7 +13301,7 @@
         <v>46</v>
       </c>
       <c r="C77" s="3">
-        <v>45.703199999999903</v>
+        <v>45.7</v>
       </c>
       <c r="D77" s="8">
         <v>2744</v>
@@ -12525,7 +13317,7 @@
         <v>26</v>
       </c>
       <c r="C78" s="3">
-        <v>25.699200000000001</v>
+        <v>25.7</v>
       </c>
       <c r="D78" s="8">
         <v>1539</v>
@@ -12541,7 +13333,7 @@
         <v>16</v>
       </c>
       <c r="C79" s="3">
-        <v>15.092799999999899</v>
+        <v>15.09</v>
       </c>
       <c r="D79" s="8">
         <v>906</v>
@@ -12557,7 +13349,7 @@
         <v>41</v>
       </c>
       <c r="C80" s="3">
-        <v>40.488100000000003</v>
+        <v>40.49</v>
       </c>
       <c r="D80" s="8">
         <v>2430</v>
@@ -12573,7 +13365,7 @@
         <v>15</v>
       </c>
       <c r="C81" s="3">
-        <v>14.425799999999899</v>
+        <v>14.43</v>
       </c>
       <c r="D81" s="8">
         <v>866</v>
@@ -12589,7 +13381,7 @@
         <v>3</v>
       </c>
       <c r="C82" s="3">
-        <v>2.9529999999999998</v>
+        <v>2.95</v>
       </c>
       <c r="D82" s="8">
         <v>177</v>
@@ -12605,7 +13397,7 @@
         <v>30</v>
       </c>
       <c r="C83" s="3">
-        <v>29.258999999999901</v>
+        <v>29.26</v>
       </c>
       <c r="D83" s="8">
         <v>1753</v>
@@ -12621,7 +13413,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="3">
-        <v>4.4523999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="D84" s="8">
         <v>268</v>
@@ -12637,7 +13429,7 @@
         <v>19</v>
       </c>
       <c r="C85" s="3">
-        <v>18.586200000000002</v>
+        <v>18.59</v>
       </c>
       <c r="D85" s="8">
         <v>1116</v>
@@ -12653,7 +13445,7 @@
         <v>4</v>
       </c>
       <c r="C86" s="3">
-        <v>3.1151</v>
+        <v>3.12</v>
       </c>
       <c r="D86" s="8">
         <v>187</v>
@@ -12669,7 +13461,7 @@
         <v>32</v>
       </c>
       <c r="C87" s="3">
-        <v>31.797599999999999</v>
+        <v>31.8</v>
       </c>
       <c r="D87" s="8">
         <v>1910</v>
@@ -12685,7 +13477,7 @@
         <v>17</v>
       </c>
       <c r="C88" s="3">
-        <v>16.2242</v>
+        <v>16.22</v>
       </c>
       <c r="D88" s="8">
         <v>974</v>
@@ -12701,7 +13493,7 @@
         <v>36</v>
       </c>
       <c r="C89" s="3">
-        <v>35.637799999999899</v>
+        <v>35.64</v>
       </c>
       <c r="D89" s="8">
         <v>2141</v>
@@ -12717,7 +13509,7 @@
         <v>7</v>
       </c>
       <c r="C90" s="3">
-        <v>6.7108999999999996</v>
+        <v>6.71</v>
       </c>
       <c r="D90" s="8">
         <v>403</v>
@@ -12733,7 +13525,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="3">
-        <v>3.0407999999999999</v>
+        <v>3.04</v>
       </c>
       <c r="D91" s="8">
         <v>183</v>
@@ -12749,7 +13541,7 @@
         <v>17</v>
       </c>
       <c r="C92" s="3">
-        <v>16.503799999999998</v>
+        <v>16.5</v>
       </c>
       <c r="D92" s="8">
         <v>990</v>
@@ -12765,7 +13557,7 @@
         <v>4</v>
       </c>
       <c r="C93" s="3">
-        <v>3.2988</v>
+        <v>3.3</v>
       </c>
       <c r="D93" s="8">
         <v>198</v>
@@ -12781,7 +13573,7 @@
         <v>51</v>
       </c>
       <c r="C94" s="3">
-        <v>50.044199999999996</v>
+        <v>50.04</v>
       </c>
       <c r="D94" s="8">
         <v>3001</v>
@@ -12797,7 +13589,7 @@
         <v>45</v>
       </c>
       <c r="C95" s="3">
-        <v>44.579799999999999</v>
+        <v>44.58</v>
       </c>
       <c r="D95" s="8">
         <v>2673</v>
@@ -12813,7 +13605,7 @@
         <v>2</v>
       </c>
       <c r="C96" s="3">
-        <v>1.3923000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="D96" s="3">
         <v>84</v>
@@ -12828,7 +13620,7 @@
         <v>7</v>
       </c>
       <c r="C97" s="3">
-        <v>6.5819999999999999</v>
+        <v>6.58</v>
       </c>
       <c r="D97" s="3">
         <v>395</v>
@@ -12843,7 +13635,7 @@
         <v>80</v>
       </c>
       <c r="C98" s="3">
-        <v>79.885400000000004</v>
+        <v>79.89</v>
       </c>
       <c r="D98" s="3">
         <v>4794</v>
@@ -12858,7 +13650,7 @@
         <v>32</v>
       </c>
       <c r="C99" s="3">
-        <v>31.671900000000001</v>
+        <v>31.67</v>
       </c>
       <c r="D99" s="3">
         <v>1902</v>
@@ -12873,7 +13665,7 @@
         <v>11</v>
       </c>
       <c r="C100" s="3">
-        <v>10.263999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="D100" s="3">
         <v>616</v>
@@ -12888,7 +13680,7 @@
         <v>65</v>
       </c>
       <c r="C101" s="3">
-        <v>64.005799999999994</v>
+        <v>64.010000000000005</v>
       </c>
       <c r="D101" s="3">
         <v>3840</v>
@@ -12903,7 +13695,7 @@
         <v>13</v>
       </c>
       <c r="C102" s="3">
-        <v>12.5575999999999</v>
+        <v>12.56</v>
       </c>
       <c r="D102" s="3">
         <v>754</v>
@@ -12918,7 +13710,7 @@
         <v>4</v>
       </c>
       <c r="C103" s="3">
-        <v>3.3315999999999999</v>
+        <v>3.33</v>
       </c>
       <c r="D103" s="3">
         <v>200</v>
@@ -12933,7 +13725,7 @@
         <v>8</v>
       </c>
       <c r="C104" s="3">
-        <v>7.2776999999999896</v>
+        <v>7.28</v>
       </c>
       <c r="D104" s="3">
         <v>437</v>
@@ -12948,7 +13740,7 @@
         <v>26</v>
       </c>
       <c r="C105" s="3">
-        <v>25.246699999999901</v>
+        <v>25.25</v>
       </c>
       <c r="D105" s="3">
         <v>1515</v>
@@ -12963,7 +13755,7 @@
         <v>4</v>
       </c>
       <c r="C106" s="3">
-        <v>3.1345999999999998</v>
+        <v>3.13</v>
       </c>
       <c r="D106" s="3">
         <v>189</v>
@@ -12978,7 +13770,7 @@
         <v>10</v>
       </c>
       <c r="C107" s="3">
-        <v>9.0386999999999897</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="D107" s="3">
         <v>544</v>
@@ -12993,7 +13785,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="3">
-        <v>4.1421999999999999</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="D108" s="3">
         <v>248</v>
@@ -13008,7 +13800,7 @@
         <v>3</v>
       </c>
       <c r="C109" s="3">
-        <v>2.9584999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="D109" s="3">
         <v>178</v>
@@ -13023,7 +13815,7 @@
         <v>3</v>
       </c>
       <c r="C110" s="3">
-        <v>2.8536999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="D110" s="3">
         <v>171</v>
@@ -13038,7 +13830,7 @@
         <v>4</v>
       </c>
       <c r="C111" s="3">
-        <v>3.355</v>
+        <v>3.35</v>
       </c>
       <c r="D111" s="3">
         <v>201</v>
@@ -13053,7 +13845,7 @@
         <v>20</v>
       </c>
       <c r="C112" s="3">
-        <v>19.3887999999999</v>
+        <v>19.39</v>
       </c>
       <c r="D112" s="3">
         <v>1162</v>
@@ -13068,7 +13860,7 @@
         <v>16</v>
       </c>
       <c r="C113" s="3">
-        <v>15.337399999999899</v>
+        <v>15.34</v>
       </c>
       <c r="D113" s="3">
         <v>921</v>
@@ -13083,7 +13875,7 @@
         <v>6</v>
       </c>
       <c r="C114" s="3">
-        <v>5.9333</v>
+        <v>5.93</v>
       </c>
       <c r="D114" s="3">
         <v>357</v>
@@ -13098,7 +13890,7 @@
         <v>4</v>
       </c>
       <c r="C115" s="3">
-        <v>3.0655999999999999</v>
+        <v>3.07</v>
       </c>
       <c r="D115" s="3">
         <v>184</v>
@@ -13113,7 +13905,7 @@
         <v>4</v>
       </c>
       <c r="C116" s="3">
-        <v>3.6802999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="D116" s="3">
         <v>220</v>
@@ -13128,7 +13920,7 @@
         <v>13</v>
       </c>
       <c r="C117" s="3">
-        <v>12.242000000000001</v>
+        <v>12.24</v>
       </c>
       <c r="D117" s="3">
         <v>735</v>
@@ -13143,7 +13935,7 @@
         <v>3</v>
       </c>
       <c r="C118" s="3">
-        <v>2.9768999999999899</v>
+        <v>2.98</v>
       </c>
       <c r="D118" s="3">
         <v>178</v>
@@ -13158,7 +13950,7 @@
         <v>14</v>
       </c>
       <c r="C119" s="3">
-        <v>13.650399999999999</v>
+        <v>13.65</v>
       </c>
       <c r="D119" s="3">
         <v>819</v>
@@ -13173,7 +13965,7 @@
         <v>9</v>
       </c>
       <c r="C120" s="3">
-        <v>8.0946999999999996</v>
+        <v>8.09</v>
       </c>
       <c r="D120" s="3">
         <v>486</v>
@@ -13188,7 +13980,7 @@
         <v>8</v>
       </c>
       <c r="C121" s="3">
-        <v>7.3889999999999896</v>
+        <v>7.39</v>
       </c>
       <c r="D121" s="3">
         <v>444</v>
@@ -13203,7 +13995,7 @@
         <v>22</v>
       </c>
       <c r="C122" s="3">
-        <v>21.929600000000001</v>
+        <v>21.93</v>
       </c>
       <c r="D122" s="3">
         <v>1316</v>
@@ -13214,11 +14006,11 @@
         <v>46110</v>
       </c>
       <c r="B123" s="9">
-        <f>ROUNDUP(C123, 0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="C123" s="3">
-        <v>2.8683000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="D123" s="3">
         <v>172</v>
@@ -13233,10 +14025,355 @@
         <v>4</v>
       </c>
       <c r="C124" s="3">
-        <v>3.5411000000000001</v>
+        <v>3.54</v>
       </c>
       <c r="D124" s="3">
         <v>212</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B125" s="9">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="C125" s="3">
+        <v>29.08</v>
+      </c>
+      <c r="D125" s="3">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B126" s="9">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C126" s="3">
+        <v>3.08</v>
+      </c>
+      <c r="D126" s="3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B127" s="9">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C127" s="3">
+        <v>3.33</v>
+      </c>
+      <c r="D127" s="3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B128" s="9">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C128" s="3">
+        <v>3.65</v>
+      </c>
+      <c r="D128" s="3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B129" s="9">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="C129" s="3">
+        <v>13.05</v>
+      </c>
+      <c r="D129" s="3">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B130" s="9">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C130" s="3">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="D130" s="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B131" s="9">
+        <f t="shared" ref="B131:B147" si="2">ROUNDUP(C131,0)</f>
+        <v>4</v>
+      </c>
+      <c r="C131" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="D131" s="3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B132" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C132" s="3">
+        <v>2.65</v>
+      </c>
+      <c r="D132" s="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B133" s="9">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="C133" s="3">
+        <v>11.65</v>
+      </c>
+      <c r="D133" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B134" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C134" s="3">
+        <v>3.42</v>
+      </c>
+      <c r="D134" s="3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B135" s="9">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C135" s="3">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="D135" s="3">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B136" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C136" s="3">
+        <v>2.97</v>
+      </c>
+      <c r="D136" s="3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B137" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C137" s="3">
+        <v>3.17</v>
+      </c>
+      <c r="D137" s="3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B138" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C138" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="D138" s="3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B139" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C139" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="D139" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B140" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C140" s="3">
+        <v>3.55</v>
+      </c>
+      <c r="D140" s="3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B141" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C141" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="D141" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B142" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C142" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="D142" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B143" s="9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C143" s="3">
+        <v>2.97</v>
+      </c>
+      <c r="D143" s="3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B144" s="9">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C144" s="3">
+        <v>5.16</v>
+      </c>
+      <c r="D144" s="3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B145" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C145" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="D145" s="3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B146" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C146" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="D146" s="3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B147" s="9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C147" s="3">
+        <v>3.38</v>
+      </c>
+      <c r="D147" s="3">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -13289,7 +14426,7 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E13" s="13"/>
     </row>
@@ -13298,7 +14435,7 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E14" s="14"/>
     </row>
@@ -13307,7 +14444,7 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -13315,7 +14452,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="E16" s="13"/>
     </row>
@@ -13324,7 +14461,7 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>1556</v>
+        <v>1615</v>
       </c>
       <c r="E17" s="14"/>
     </row>
@@ -13629,7 +14766,7 @@
         <v>82</v>
       </c>
       <c r="B36">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -13637,7 +14774,7 @@
         <v>81</v>
       </c>
       <c r="B37">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -13789,7 +14926,7 @@
         <v>101</v>
       </c>
       <c r="B56">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">

--- a/Aji_game copy_February.xlsx
+++ b/Aji_game copy_February.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v2.0" hidden="1">User_funnel!$A$2:$A$4</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">User_funnel!$B$2:$B$4</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">User_funnel!$D$2:$D$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1086,12 +1086,12 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'User Engagement'!$A$36:$A$94</c:f>
+              <c:f>'User Engagement'!$A$95:$A$145</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'User Engagement'!$B$36:$B$94</c:f>
+              <c:f>'User Engagement'!$B$95:$B$145</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1133,12 +1133,12 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'User Engagement'!$A$36:$A$94</c:f>
+              <c:f>'User Engagement'!$A$95:$A$145</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'User Engagement'!$C$36:$C$94</c:f>
+              <c:f>'User Engagement'!$C$95:$C$145</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1350,336 +1350,8 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-TH"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'gameplay_report(score) '!$B$1</c:f>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-                <a:miter lim="800000"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-TH"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>'gameplay_report(score) '!$A$67:$A$94</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'gameplay_report(score) '!$B$67:$B$94</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6386-F942-8A1B-A2D1B6C2E5A6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1311679680"/>
-        <c:axId val="1351481792"/>
-      </c:lineChart>
-      <c:dateAx>
-        <c:axId val="1311679680"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-TH"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1351481792"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-      </c:dateAx>
-      <c:valAx>
-        <c:axId val="1351481792"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0,&quot;k&quot;" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-TH"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1311679680"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-TH"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart"><c:date1904 val="0"/><c:lang val="en-US"/><c:roundedCorners val="0"/><mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006"><mc:Choice Requires="c14" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart"><c14:style val="102"/></mc:Choice><mc:Fallback><c:style val="2"/></mc:Fallback></mc:AlternateContent><c:chart><c:title><c:overlay val="0"/><c:spPr><a:noFill/><a:ln><a:noFill/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/><a:lstStyle/><a:p><a:pPr><a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="65000"/><a:lumOff val="35000"/></a:schemeClr></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr></c:title><c:autoTitleDeleted val="0"/><c:plotArea><c:layout/><c:lineChart><c:grouping val="standard"/><c:varyColors val="0"/><c:ser><c:idx val="0"/><c:order val="0"/><c:tx><c:strRef><c:f>'gameplay_report(score) '!$B$1</c:f></c:strRef></c:tx><c:spPr><a:ln w="28575" cap="rnd"><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr><c:marker><c:symbol val="circle"/><c:size val="5"/><c:spPr><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:ln w="9525"><a:solidFill><a:schemeClr val="accent3"/></a:solidFill></a:ln><a:effectLst/></c:spPr></c:marker><c:dLbls><c:spPr><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:ln w="19050" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:prstDash val="solid"/><a:miter lim="800000"/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"><a:spAutoFit/></a:bodyPr><a:lstStyle/><a:p><a:pPr><a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"><a:solidFill><a:schemeClr val="bg1"/></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:dLblPos val="t"/><c:showLegendKey val="0"/><c:showVal val="1"/><c:showCatName val="0"/><c:showSerName val="0"/><c:showPercent val="0"/><c:showBubbleSize val="0"/><c:showLeaderLines val="0"/><c:extLst><c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"><c15:showLeaderLines val="1"/><c15:leaderLines><c:spPr><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="35000"/><a:lumOff val="65000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr></c15:leaderLines></c:ext></c:extLst></c:dLbls><c:cat><c:numRef><c:f>'gameplay_report(score) '!$A$67:$A$94</c:f></c:numRef></c:cat><c:val><c:numRef><c:f>'gameplay_report(score) '!$B$67:$B$94</c:f></c:numRef></c:val><c:smooth val="0"/><c:extLst><c:ext uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}" xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart"><c16:uniqueId val="{00000000-6386-F942-8A1B-A2D1B6C2E5A6}"/></c:ext></c:extLst></c:ser><c:dLbls><c:dLblPos val="t"/><c:showLegendKey val="0"/><c:showVal val="1"/><c:showCatName val="0"/><c:showSerName val="0"/><c:showPercent val="0"/><c:showBubbleSize val="0"/></c:dLbls><c:marker val="1"/><c:smooth val="0"/><c:axId val="1311679680"/><c:axId val="1351481792"/></c:lineChart><c:dateAx><c:axId val="1311679680"/><c:scaling><c:orientation val="minMax"/></c:scaling><c:delete val="0"/><c:axPos val="b"/><c:numFmt formatCode="m/d/yy" sourceLinked="1"/><c:majorTickMark val="out"/><c:minorTickMark val="none"/><c:tickLblPos val="nextTo"/><c:spPr><a:noFill/><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="15000"/><a:lumOff val="85000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/><a:lstStyle/><a:p><a:pPr><a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="65000"/><a:lumOff val="35000"/></a:schemeClr></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:crossAx val="1351481792"/><c:crosses val="autoZero"/><c:auto val="1"/><c:lblOffset val="100"/><c:baseTimeUnit val="days"/></c:dateAx><c:valAx><c:axId val="1351481792"/><c:scaling><c:orientation val="minMax"/></c:scaling><c:delete val="0"/><c:axPos val="l"/><c:majorGridlines><c:spPr><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="15000"/><a:lumOff val="85000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr></c:majorGridlines><c:numFmt formatCode="0,&quot;k&quot;" sourceLinked="1"/><c:majorTickMark val="none"/><c:minorTickMark val="none"/><c:tickLblPos val="nextTo"/><c:spPr><a:noFill/><a:ln><a:noFill/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/><a:lstStyle/><a:p><a:pPr><a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="65000"/><a:lumOff val="35000"/></a:schemeClr></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:crossAx val="1311679680"/><c:crosses val="autoZero"/><c:crossBetween val="between"/></c:valAx><c:spPr><a:noFill/><a:ln><a:noFill/></a:ln><a:effectLst/></c:spPr></c:plotArea><c:plotVisOnly val="1"/><c:dispBlanksAs val="gap"/><c:showDLblsOverMax val="0"/><c:extLst><c:ext uri="{56B9EC1D-385E-4148-901F-78D8002777C0}" xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart"><c16r3:dataDisplayOptions16><c16r3:dispNaAsBlank val="1"/></c16r3:dataDisplayOptions16></c:ext></c:extLst></c:chart><c:spPr><a:solidFill><a:schemeClr val="bg1"/></a:solidFill><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="15000"/><a:lumOff val="85000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr/><a:lstStyle/><a:p><a:pPr><a:defRPr/></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:printSettings><c:headerFooter/><c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/><c:pageSetup/></c:printSettings></c:chartSpace>ace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1792,12 +1464,12 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'gameplay_report(time) '!$A$36:$A$94</c:f>
+              <c:f>'gameplay_report(time) '!$A$95:$A$147</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'gameplay_report(time) '!$B$36:$B$94</c:f>
+              <c:f>'gameplay_report(time) '!$B$95:$B$147</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>

--- a/Aji_game copy_February.xlsx
+++ b/Aji_game copy_February.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v2.0" hidden="1">User_funnel!$A$2:$A$4</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">User_funnel!$D$2:$D$4</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">User_funnel!$B$2:$B$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1086,12 +1086,12 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'User Engagement'!$A$95:$A$145</c:f>
+              <c:f>'User Engagement'!$A$36:$A$94</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'User Engagement'!$B$95:$B$145</c:f>
+              <c:f>'User Engagement'!$B$36:$B$94</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1133,12 +1133,12 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'User Engagement'!$A$95:$A$145</c:f>
+              <c:f>'User Engagement'!$A$36:$A$94</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'User Engagement'!$C$95:$C$145</c:f>
+              <c:f>'User Engagement'!$C$36:$C$94</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -1350,8 +1350,336 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart"><c:date1904 val="0"/><c:lang val="en-US"/><c:roundedCorners val="0"/><mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006"><mc:Choice Requires="c14" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart"><c14:style val="102"/></mc:Choice><mc:Fallback><c:style val="2"/></mc:Fallback></mc:AlternateContent><c:chart><c:title><c:overlay val="0"/><c:spPr><a:noFill/><a:ln><a:noFill/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/><a:lstStyle/><a:p><a:pPr><a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="65000"/><a:lumOff val="35000"/></a:schemeClr></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr></c:title><c:autoTitleDeleted val="0"/><c:plotArea><c:layout/><c:lineChart><c:grouping val="standard"/><c:varyColors val="0"/><c:ser><c:idx val="0"/><c:order val="0"/><c:tx><c:strRef><c:f>'gameplay_report(score) '!$B$1</c:f></c:strRef></c:tx><c:spPr><a:ln w="28575" cap="rnd"><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr><c:marker><c:symbol val="circle"/><c:size val="5"/><c:spPr><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:ln w="9525"><a:solidFill><a:schemeClr val="accent3"/></a:solidFill></a:ln><a:effectLst/></c:spPr></c:marker><c:dLbls><c:spPr><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:ln w="19050" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="accent3"/></a:solidFill><a:prstDash val="solid"/><a:miter lim="800000"/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"><a:spAutoFit/></a:bodyPr><a:lstStyle/><a:p><a:pPr><a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"><a:solidFill><a:schemeClr val="bg1"/></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:dLblPos val="t"/><c:showLegendKey val="0"/><c:showVal val="1"/><c:showCatName val="0"/><c:showSerName val="0"/><c:showPercent val="0"/><c:showBubbleSize val="0"/><c:showLeaderLines val="0"/><c:extLst><c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"><c15:showLeaderLines val="1"/><c15:leaderLines><c:spPr><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="35000"/><a:lumOff val="65000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr></c15:leaderLines></c:ext></c:extLst></c:dLbls><c:cat><c:numRef><c:f>'gameplay_report(score) '!$A$67:$A$94</c:f></c:numRef></c:cat><c:val><c:numRef><c:f>'gameplay_report(score) '!$B$67:$B$94</c:f></c:numRef></c:val><c:smooth val="0"/><c:extLst><c:ext uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}" xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart"><c16:uniqueId val="{00000000-6386-F942-8A1B-A2D1B6C2E5A6}"/></c:ext></c:extLst></c:ser><c:dLbls><c:dLblPos val="t"/><c:showLegendKey val="0"/><c:showVal val="1"/><c:showCatName val="0"/><c:showSerName val="0"/><c:showPercent val="0"/><c:showBubbleSize val="0"/></c:dLbls><c:marker val="1"/><c:smooth val="0"/><c:axId val="1311679680"/><c:axId val="1351481792"/></c:lineChart><c:dateAx><c:axId val="1311679680"/><c:scaling><c:orientation val="minMax"/></c:scaling><c:delete val="0"/><c:axPos val="b"/><c:numFmt formatCode="m/d/yy" sourceLinked="1"/><c:majorTickMark val="out"/><c:minorTickMark val="none"/><c:tickLblPos val="nextTo"/><c:spPr><a:noFill/><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="15000"/><a:lumOff val="85000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/><a:lstStyle/><a:p><a:pPr><a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="65000"/><a:lumOff val="35000"/></a:schemeClr></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:crossAx val="1351481792"/><c:crosses val="autoZero"/><c:auto val="1"/><c:lblOffset val="100"/><c:baseTimeUnit val="days"/></c:dateAx><c:valAx><c:axId val="1351481792"/><c:scaling><c:orientation val="minMax"/></c:scaling><c:delete val="0"/><c:axPos val="l"/><c:majorGridlines><c:spPr><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="15000"/><a:lumOff val="85000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr></c:majorGridlines><c:numFmt formatCode="0,&quot;k&quot;" sourceLinked="1"/><c:majorTickMark val="none"/><c:minorTickMark val="none"/><c:tickLblPos val="nextTo"/><c:spPr><a:noFill/><a:ln><a:noFill/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/><a:lstStyle/><a:p><a:pPr><a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="65000"/><a:lumOff val="35000"/></a:schemeClr></a:solidFill><a:latin typeface="+mn-lt"/><a:ea typeface="+mn-ea"/><a:cs typeface="+mn-cs"/></a:defRPr></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:crossAx val="1311679680"/><c:crosses val="autoZero"/><c:crossBetween val="between"/></c:valAx><c:spPr><a:noFill/><a:ln><a:noFill/></a:ln><a:effectLst/></c:spPr></c:plotArea><c:plotVisOnly val="1"/><c:dispBlanksAs val="gap"/><c:showDLblsOverMax val="0"/><c:extLst><c:ext uri="{56B9EC1D-385E-4148-901F-78D8002777C0}" xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart"><c16r3:dataDisplayOptions16><c16r3:dispNaAsBlank val="1"/></c16r3:dataDisplayOptions16></c:ext></c:extLst></c:chart><c:spPr><a:solidFill><a:schemeClr val="bg1"/></a:solidFill><a:ln w="9525" cap="flat" cmpd="sng" algn="ctr"><a:solidFill><a:schemeClr val="tx1"><a:lumMod val="15000"/><a:lumOff val="85000"/></a:schemeClr></a:solidFill><a:round/></a:ln><a:effectLst/></c:spPr><c:txPr><a:bodyPr/><a:lstStyle/><a:p><a:pPr><a:defRPr/></a:pPr><a:endParaRPr lang="en-TH"/></a:p></c:txPr><c:printSettings><c:headerFooter/><c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/><c:pageSetup/></c:printSettings></c:chartSpace>ace>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-TH"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'gameplay_report(score) '!$B$1</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:miter lim="800000"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-TH"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'gameplay_report(score) '!$A$67:$A$94</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'gameplay_report(score) '!$B$67:$B$94</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6386-F942-8A1B-A2D1B6C2E5A6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1311679680"/>
+        <c:axId val="1351481792"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1311679680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-TH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1351481792"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1351481792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0,&quot;k&quot;" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-TH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1311679680"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-TH"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1464,12 +1792,12 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'gameplay_report(time) '!$A$95:$A$147</c:f>
+              <c:f>'gameplay_report(time) '!$A$36:$A$94</c:f>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'gameplay_report(time) '!$B$95:$B$147</c:f>
+              <c:f>'gameplay_report(time) '!$B$36:$B$94</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
